--- a/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,48</t>
+          <t>-1,99; 5,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 2,68</t>
+          <t>-3,37; 2,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 11,89</t>
+          <t>0,56; 12,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,98; -0,77</t>
+          <t>-7,51; -0,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,85</t>
+          <t>-4,02; 3,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 2,85</t>
+          <t>-5,21; 2,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,42</t>
+          <t>-3,29; 1,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 2,52</t>
+          <t>-2,96; 2,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 5,44</t>
+          <t>-1,17; 5,68</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-84,31; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,82; —</t>
+          <t>-42,79; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-85,76; 442,81</t>
+          <t>-86,98; 363,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 402,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-85,37; 167,88</t>
+          <t>-81,68; 237,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-73,74; 245,47</t>
+          <t>-70,77; 251,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 505,81</t>
+          <t>-37,11; 629,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,33</t>
+          <t>-1,75; 3,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,19</t>
+          <t>-1,7; 3,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 7,48</t>
+          <t>1,08; 7,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 1,29</t>
+          <t>-2,96; 1,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 6,0</t>
+          <t>-0,08; 5,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,18</t>
+          <t>0,73; 7,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 1,52</t>
+          <t>-1,92; 1,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 3,98</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,35</t>
+          <t>1,84; 6,65</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,26; 447,52</t>
+          <t>-73,02; 534,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 419,56</t>
+          <t>-75,07; 457,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,44; 1038,26</t>
+          <t>18,65; 1044,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-89,59; 161,62</t>
+          <t>-88,35; 159,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 580,99</t>
+          <t>-13,73; 526,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 682,41</t>
+          <t>5,65; 609,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,63; 142,9</t>
+          <t>-71,2; 123,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 325,46</t>
+          <t>-11,69; 294,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,43; 538,3</t>
+          <t>49,13; 526,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 5,31</t>
+          <t>-4,98; 4,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 6,18</t>
+          <t>-2,88; 5,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 7,88</t>
+          <t>-2,07; 7,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 1,03</t>
+          <t>-6,03; 0,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 6,58</t>
+          <t>-2,41; 6,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 3,68</t>
+          <t>-3,4; 4,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,97</t>
+          <t>-4,31; 1,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 5,31</t>
+          <t>-0,86; 5,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,3</t>
+          <t>-1,65; 4,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-77,44; 373,81</t>
+          <t>-78,95; 305,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,89; 443,61</t>
+          <t>-51,96; 353,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 610,08</t>
+          <t>-39,11; 508,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 267,02</t>
+          <t>-100,0; 167,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,04; 397,41</t>
+          <t>-48,85; 400,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,01; 239,14</t>
+          <t>-59,93; 304,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-76,54; 98,6</t>
+          <t>-82,46; 87,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,75; 256,82</t>
+          <t>-19,9; 245,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 193,6</t>
+          <t>-31,51; 210,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,58</t>
+          <t>-2,33; 3,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 13,18</t>
+          <t>3,27; 13,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,47</t>
+          <t>-0,68; 4,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,66</t>
+          <t>-3,07; 3,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 6,11</t>
+          <t>-1,53; 5,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 8,51</t>
+          <t>1,1; 8,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,31</t>
+          <t>-2,02; 2,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,84</t>
+          <t>2,05; 8,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,6</t>
+          <t>1,3; 6,03</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-82,59; 367,23</t>
+          <t>-82,85; 485,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>58,46; 1524,46</t>
+          <t>72,46; 1407,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 626,57</t>
+          <t>-32,6; 554,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-84,35; 250,78</t>
+          <t>-78,94; 262,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 509,94</t>
+          <t>-50,15; 475,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,35; 629,91</t>
+          <t>6,69; 650,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-63,0; 163,13</t>
+          <t>-65,76; 150,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>39,99; 522,0</t>
+          <t>50,66; 600,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>17,99; 363,93</t>
+          <t>29,36; 456,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,54</t>
+          <t>-0,82; 2,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,86</t>
+          <t>0,99; 4,77</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,98</t>
+          <t>1,49; 5,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; -0,02</t>
+          <t>-2,64; -0,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,88</t>
+          <t>0,24; 3,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,06</t>
+          <t>1,29; 4,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,74</t>
+          <t>-1,36; 0,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,81</t>
+          <t>1,08; 3,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,43</t>
+          <t>1,86; 4,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 162,54</t>
+          <t>-30,3; 154,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>31,39; 321,6</t>
+          <t>22,01; 305,45</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>39,92; 339,12</t>
+          <t>44,25; 343,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-79,12; 3,74</t>
+          <t>-76,48; 7,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,51; 207,97</t>
+          <t>5,83; 202,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,01; 269,31</t>
+          <t>35,55; 239,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 38,9</t>
+          <t>-46,46; 37,6</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>38,33; 195,61</t>
+          <t>35,97; 184,39</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>60,49; 224,23</t>
+          <t>58,08; 229,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 5,39</t>
+          <t>-1,75; 6,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 2,63</t>
+          <t>-3,49; 2,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 12,28</t>
+          <t>0,63; 11,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,51; -0,78</t>
+          <t>-7,28; -0,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 3,71</t>
+          <t>-4,58; 3,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,75</t>
+          <t>-4,83; 2,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,55</t>
+          <t>-3,27; 1,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 2,39</t>
+          <t>-2,89; 2,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 5,68</t>
+          <t>-1,0; 5,86</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,79; —</t>
+          <t>-20,18; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -803,27 +803,27 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,98; 363,56</t>
+          <t>-91,45; 538,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 402,11</t>
+          <t>-100,0; 489,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,68; 237,1</t>
+          <t>-85,27; 207,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,77; 251,88</t>
+          <t>-76,36; 257,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 629,62</t>
+          <t>-38,79; 514,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,44</t>
+          <t>-1,64; 3,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 3,32</t>
+          <t>-1,76; 3,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 7,7</t>
+          <t>1,28; 7,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,01</t>
+          <t>-3,21; 1,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 5,75</t>
+          <t>-0,28; 5,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,1</t>
+          <t>0,65; 7,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,44</t>
+          <t>-1,74; 1,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,03; 4,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,65</t>
+          <t>1,69; 6,32</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-73,02; 534,92</t>
+          <t>-72,32; 420,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 457,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,65; 1044,3</t>
+          <t>23,74; 1150,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-88,35; 159,83</t>
+          <t>-87,06; 193,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 526,89</t>
+          <t>-16,82; 545,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 609,55</t>
+          <t>1,95; 675,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 123,44</t>
+          <t>-65,83; 141,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 294,71</t>
+          <t>-9,03; 320,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,13; 526,21</t>
+          <t>53,14; 514,19</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 4,76</t>
+          <t>-4,52; 5,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 5,84</t>
+          <t>-2,95; 6,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 7,69</t>
+          <t>-2,01; 7,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 0,88</t>
+          <t>-6,54; 0,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 6,7</t>
+          <t>-2,42; 6,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 4,5</t>
+          <t>-4,17; 4,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 1,7</t>
+          <t>-4,12; 1,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 5,6</t>
+          <t>-0,91; 5,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,38</t>
+          <t>-1,57; 4,49</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,95; 305,66</t>
+          <t>-76,8; 404,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 353,42</t>
+          <t>-50,06; 403,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-39,11; 508,97</t>
+          <t>-43,19; 447,63</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 167,61</t>
+          <t>-100,0; 223,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,85; 400,97</t>
+          <t>-49,54; 460,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 304,39</t>
+          <t>-66,27; 257,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-82,46; 87,0</t>
+          <t>-73,07; 95,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 245,55</t>
+          <t>-19,82; 223,93</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,51; 210,1</t>
+          <t>-28,16; 186,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 3,78</t>
+          <t>-2,52; 3,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 13,29</t>
+          <t>3,9; 13,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,81</t>
+          <t>-0,9; 4,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 3,02</t>
+          <t>-3,08; 2,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 5,81</t>
+          <t>-1,73; 5,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,45</t>
+          <t>1,33; 8,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,2</t>
+          <t>-1,94; 2,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,05; 8,24</t>
+          <t>2,12; 8,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,03</t>
+          <t>1,12; 5,86</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-82,85; 485,69</t>
+          <t>-80,8; 476,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>72,46; 1407,6</t>
+          <t>73,33; 1352,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 554,21</t>
+          <t>-32,17; 543,62</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-78,94; 262,56</t>
+          <t>-80,57; 221,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 475,67</t>
+          <t>-51,11; 489,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,69; 650,87</t>
+          <t>20,27; 761,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,76; 150,95</t>
+          <t>-60,44; 163,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,66; 600,66</t>
+          <t>57,96; 617,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29,36; 456,62</t>
+          <t>19,7; 393,57</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,5</t>
+          <t>-0,65; 2,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,77</t>
+          <t>1,1; 4,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,04</t>
+          <t>1,33; 4,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,01</t>
+          <t>-2,78; 0,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,91</t>
+          <t>0,31; 3,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,83</t>
+          <t>1,23; 4,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,73</t>
+          <t>-1,39; 0,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,65</t>
+          <t>1,11; 3,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,41</t>
+          <t>1,82; 4,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,3; 154,55</t>
+          <t>-26,67; 173,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>22,01; 305,45</t>
+          <t>35,41; 337,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44,25; 343,91</t>
+          <t>35,65; 337,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-76,48; 7,11</t>
+          <t>-76,8; 11,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,83; 202,8</t>
+          <t>1,29; 197,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>35,55; 239,55</t>
+          <t>33,31; 259,85</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,46; 37,6</t>
+          <t>-46,86; 36,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>35,97; 184,39</t>
+          <t>37,86; 204,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>58,08; 229,53</t>
+          <t>56,49; 225,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,05</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,04</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,12</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,05</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,13</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>5,04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,99</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 6,21</t>
+          <t>-6,98; -0,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,56</t>
+          <t>-4,1; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 11,71</t>
+          <t>-5,39; 2,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; -0,78</t>
+          <t>-1,88; 5,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 3,73</t>
+          <t>-3,33; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 2,83</t>
+          <t>0,59; 11,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,54</t>
+          <t>-3,37; 1,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,36</t>
+          <t>-2,62; 2,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 5,86</t>
+          <t>-1,07; 5,58</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-4,2%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-34,07%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>109,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>315,7%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-4,2%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-29,42%</t>
+          <t>310,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,81%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-85,76; 442,81</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-20,18; —</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-84,31; —</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-91,45; 538,61</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 489,86</t>
+          <t>-45,9; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-85,27; 207,95</t>
+          <t>-85,37; 167,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-76,36; 257,02</t>
+          <t>-73,74; 245,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 514,01</t>
+          <t>-40,55; 517,55</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,76</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,81</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3,53</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,55</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,7</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,13</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,81</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,63</t>
+          <t>4,71</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>4,1</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,05</t>
+          <t>-3,26; 1,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,12</t>
+          <t>0,17; 6,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,74</t>
+          <t>0,64; 7,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,04</t>
+          <t>-1,64; 3,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 5,77</t>
+          <t>-1,65; 3,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 7,36</t>
+          <t>1,47; 8,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,57</t>
+          <t>-1,82; 1,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,06</t>
+          <t>-0,15; 3,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,32</t>
+          <t>1,94; 6,62</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-35,63%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>132,06%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>165,54%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>32,05%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>40,3%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>239,09%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-35,63%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>132,06%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>170,19%</t>
+          <t>272,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>200,73%</t>
+          <t>212,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-72,32; 420,59</t>
+          <t>-89,59; 161,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,61; 580,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23,74; 1150,14</t>
+          <t>-0,3; 682,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,06; 193,54</t>
+          <t>-69,26; 447,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 545,19</t>
+          <t>-71,29; 419,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 675,99</t>
+          <t>20,11; 1167,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,83; 141,26</t>
+          <t>-66,63; 142,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 320,58</t>
+          <t>-15,06; 325,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>53,14; 514,19</t>
+          <t>48,91; 536,75</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,33</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,84</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,08</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,09</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,28</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,53</t>
+          <t>3,66</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,68</t>
+          <t>2,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 5,16</t>
+          <t>-6,08; 1,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 6,13</t>
+          <t>-2,73; 6,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 7,5</t>
+          <t>-3,46; 4,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 0,99</t>
+          <t>-4,21; 5,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 6,86</t>
+          <t>-2,92; 6,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,06</t>
+          <t>-1,36; 8,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 1,87</t>
+          <t>-4,24; 1,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 5,07</t>
+          <t>-0,86; 5,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 4,49</t>
+          <t>-1,11; 4,94</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-60,93%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62,32%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>10,8%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>53,69%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>79,92%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-60,93%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>62,32%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 404,65</t>
+          <t>-100,0; 267,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 403,17</t>
+          <t>-48,04; 397,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 447,63</t>
+          <t>-61,78; 259,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 223,12</t>
+          <t>-77,44; 373,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 460,99</t>
+          <t>-48,89; 443,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,27; 257,2</t>
+          <t>-26,06; 667,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,07; 95,77</t>
+          <t>-76,54; 98,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,82; 223,93</t>
+          <t>-18,75; 256,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,16; 186,44</t>
+          <t>-22,16; 221,65</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,84</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>7,9</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,84</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,46</t>
+          <t>3,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,6</t>
+          <t>-3,36; 2,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,9; 13,4</t>
+          <t>-1,49; 6,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 4,62</t>
+          <t>1,48; 9,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,95</t>
+          <t>-2,42; 3,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,77</t>
+          <t>3,53; 13,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,57</t>
+          <t>-0,42; 5,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,34</t>
+          <t>-2,17; 2,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,12; 8,21</t>
+          <t>1,82; 7,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,86</t>
+          <t>1,51; 6,14</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-5,25%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>70,23%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>203,69%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>17,08%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>378,84%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>87,41%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-5,25%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>70,23%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>187,34%</t>
+          <t>110,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>147,25%</t>
+          <t>167,78%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-80,8; 476,36</t>
+          <t>-84,35; 250,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73,33; 1352,09</t>
+          <t>-55,76; 509,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,17; 543,62</t>
+          <t>13,07; 653,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-80,57; 221,51</t>
+          <t>-82,59; 367,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,11; 489,61</t>
+          <t>58,46; 1524,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,27; 761,93</t>
+          <t>-22,04; 675,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-60,44; 163,53</t>
+          <t>-63,0; 163,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>57,96; 617,27</t>
+          <t>39,99; 522,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,7; 393,57</t>
+          <t>37,32; 411,43</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,01</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,31</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2,82</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3,23</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,01</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,02</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,52</t>
+          <t>-2,86; -0,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,81</t>
+          <t>0,29; 3,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,99</t>
+          <t>1,39; 5,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,11</t>
+          <t>-0,74; 2,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,96</t>
+          <t>1,05; 4,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,99</t>
+          <t>1,77; 5,51</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,73</t>
+          <t>-1,34; 0,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,78</t>
+          <t>1,19; 3,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,57</t>
+          <t>2,2; 4,93</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-49,76%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>73,52%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>120,94%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>36,1%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>128,97%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>147,72%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-49,76%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>73,52%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>110,54%</t>
+          <t>171,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>126,91%</t>
+          <t>142,73%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-26,67; 173,05</t>
+          <t>-79,12; 3,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>35,41; 337,16</t>
+          <t>4,51; 207,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35,65; 337,08</t>
+          <t>33,89; 288,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 11,51</t>
+          <t>-26,92; 162,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,29; 197,57</t>
+          <t>31,39; 321,6</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,31; 259,85</t>
+          <t>51,6; 361,0</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,86; 36,23</t>
+          <t>-44,46; 38,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>37,86; 204,28</t>
+          <t>38,33; 195,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>56,49; 225,4</t>
+          <t>72,17; 249,98</t>
         </is>
       </c>
     </row>
